--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125681044</v>
+        <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105376</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt förvildad från trädgårdskompost</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125681081</v>
+        <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105853</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>221423</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ung planta</t>
+          <t>rikligt förvildad från trädgårdskompost</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125681019</v>
+        <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>105205</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1006,37 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680994</v>
+        <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,12 +1065,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1113,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125680976</v>
+        <v>125680994</v>
       </c>
       <c r="B6" t="n">
-        <v>91219</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5321</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1197,23 +1178,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1231,37 +1201,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125680996</v>
+        <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>58026</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103037</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,6 +1272,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ung planta</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105260</v>
+        <v>105267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105431</v>
+        <v>105438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>91273</v>
+        <v>91280</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105908</v>
+        <v>105915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105267</v>
+        <v>105270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105438</v>
+        <v>105441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>58044</v>
+        <v>58045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>91280</v>
+        <v>91281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>125680994</v>
       </c>
       <c r="B6" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105915</v>
+        <v>105918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105270</v>
+        <v>105274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105441</v>
+        <v>105445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>58045</v>
+        <v>91285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,12 +963,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>91281</v>
+        <v>58045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,23 +1076,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105918</v>
+        <v>105922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105274</v>
+        <v>105275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105445</v>
+        <v>105446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>91285</v>
+        <v>58045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,23 +963,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -997,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>58045</v>
+        <v>91285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,12 +1065,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105922</v>
+        <v>105923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105275</v>
+        <v>105277</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105446</v>
+        <v>105448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>58045</v>
+        <v>91287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,12 +963,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>91285</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,23 +1076,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
         <v>125680994</v>
       </c>
       <c r="B6" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105923</v>
+        <v>105925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105277</v>
+        <v>105279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105448</v>
+        <v>105450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>91287</v>
+        <v>58046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,23 +963,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -997,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>91289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,12 +1065,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105925</v>
+        <v>105927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105279</v>
+        <v>105283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105450</v>
+        <v>105454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>91291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,12 +963,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>91289</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,23 +1076,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105927</v>
+        <v>105931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105283</v>
+        <v>105296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105454</v>
+        <v>105467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>58050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>125680994</v>
       </c>
       <c r="B6" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>58050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,23 +963,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -997,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>58050</v>
+        <v>91295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,12 +1065,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105296</v>
+        <v>105299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105467</v>
+        <v>105470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>58050</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,12 +963,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>91295</v>
+        <v>58050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,23 +1076,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125681019</v>
+        <v>125680976</v>
       </c>
       <c r="B2" t="n">
-        <v>105299</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -754,12 +754,23 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -777,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125681044</v>
+        <v>115162690</v>
       </c>
       <c r="B3" t="n">
-        <v>105470</v>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +799,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221423</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sträckande O</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Charlottenberg nära Fiskartorpet, Upl</t>
+          <t>På vägen, Garnsviken Sigtuna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655279</v>
+        <v>655225</v>
       </c>
       <c r="R3" t="n">
-        <v>6615310</v>
+        <v>6615286</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,17 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt förvildad från trädgårdskompost</t>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,31 +895,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Örjan Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Örjan Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680976</v>
+        <v>125680994</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>58439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,23 +990,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1000,7 +1016,7 @@
         <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>58050</v>
+        <v>58353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125680994</v>
+        <v>125681061</v>
       </c>
       <c r="B6" t="n">
-        <v>58135</v>
+        <v>61491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>106670</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,6 +1186,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>förvildad planta</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1225,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105947</v>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,6 +1326,317 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125680935</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Charlottenberg nära Fiskartorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>655238</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6615297</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>igenväxt gräsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125681019</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Charlottenberg nära Fiskartorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>655279</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6615310</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125681044</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Charlottenberg nära Fiskartorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>655279</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6615310</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>rikligt förvildad från trädgårdskompost</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51848-2024 artfynd.xlsx
+++ b/artfynd/A 51848-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125680976</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115162690</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125680994</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125680996</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681061</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681081</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125680935</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681019</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,8 +1682,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681044</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>